--- a/www/flightdata/xlsx/eoss-296.xlsx
+++ b/www/flightdata/xlsx/eoss-296.xlsx
@@ -3666,7 +3666,7 @@
         <v>31706.21</v>
       </c>
       <c r="I2">
-        <v>632</v>
+        <v>474</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
